--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>64526.6875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>65422.140625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>895.453125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.368731008257191</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9206163201481231</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>64976.140625</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>64754.011719,64713.316406,64675.367188,64651.386719,64588.902344,64526.687500</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>64214.238281,64944.011719,65551.007812,65085.019531,65213.050781,65422.140625</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>539.773438,230.695313,875.640625,433.632812,624.148437,895.453125</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.840582,0.355222,1.335816,0.666256,0.957091,1.368731</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9206163201481231</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>64723.289062,64688.914062,64617.585938,64555.539062,64514.328125,64404.074219</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>64480.742188,64355.609375,64253.734375,64160.640625,64051.605469,63939.378906</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>65277.562500,65216.781250,65134.453125,65075.976562,65013.398438,64976.140625</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>65233.414062,65194.929688,65060.250000,64966.968750,64903.820312,64794.984375</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>64617.085938,64463.835938,64271.039062,64141.906250,63995.601562,63899.492188</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>64895.656250,64772.656250,64623.593750,64512.695312,64403.640625,64323.414062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>64976.140625</v>
+      </c>
+      <c r="G3" t="n">
+        <v>66241.46875</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1265.328125</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.910175225394591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.875081245186621</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66180.015625</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>65277.562500,65216.781250,65134.453125,65075.976562,65013.398438,64976.140625</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>66143.031250,66309.468750,66648.398438,66415.437500,66405.007812,66241.468750</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>865.468750,1092.687500,1513.945312,1339.460938,1391.609375,1265.328125</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.308481,1.647860,2.271540,2.016792,2.095639,1.910175</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.875081245186621</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>65233.414062,65194.929688,65060.250000,64966.968750,64903.820312,64794.984375</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>64895.656250,64772.656250,64623.593750,64512.695312,64403.640625,64323.414062</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:30:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66247.281250,66212.476562,66197.734375,66197.281250,66196.429688,66180.015625</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>66209.937500,66141.304688,66049.679688,66070.812500,66030.718750,65982.976562</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>65473.171875,65341.351562,65237.992188,65137.000000,65056.156250,64990.218750</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>65759.382812,65684.914062,65601.320312,65561.445312,65470.710938,65414.773438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>66180.015625</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65647.7734375</v>
+      </c>
+      <c r="H4" t="n">
+        <v>532.2421875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8107543632180023</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4577375515420047</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65548.375</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>66247.281250,66212.476562,66197.734375,66197.281250,66196.429688,66180.015625</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>65795.273438,65972.500000,66020.039062,65900.992188,66086.609375,65647.773438</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>452.007812,239.976562,177.695312,296.289062,109.820313,532.242188</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.686991,0.363752,0.269154,0.449597,0.166176,0.810754</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4577375515420047</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>66209.937500,66141.304688,66049.679688,66070.812500,66030.718750,65982.976562</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>65759.382812,65684.914062,65601.320312,65561.445312,65470.710938,65414.773438</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:35:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>65691.695312,65670.515625,65667.648438,65631.585938,65610.023438,65548.375000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>65602.093750,65637.023438,65561.078125,65610.718750,65508.886719,65392.503906</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65009.003906,64845.539062,64694.957031,64518.800781,64370.468750,64219.675781</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>65277.164062,65173.953125,65066.722656,64975.660156,64853.042969,64710.132812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>65548.375</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65297.73046875</v>
+      </c>
+      <c r="H5" t="n">
+        <v>250.64453125</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3838487638861395</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7369166033921399</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65216.22265625</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>65691.695312,65670.515625,65667.648438,65631.585938,65610.023438,65548.375000</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>65394.808594,65525.218750,64898.250000,64778.218750,65051.230469,65297.730469</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>296.886718,145.296875,769.398438,853.367188,558.792969,250.644531</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.453991,0.221742,1.185546,1.317367,0.859004,0.383849</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7369166033921399</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>65602.093750,65637.023438,65561.078125,65610.718750,65508.886719,65392.503906</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>65277.164062,65173.953125,65066.722656,64975.660156,64853.042969,64710.132812</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65269.843750,65241.605469,65240.070312,65211.808594,65250.128906,65216.222656</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>65178.515625,65221.792969,65206.812500,65201.917969,65111.105469,65076.378906</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>64664.433594,64461.421875,64302.183594,64102.140625,64012.519531,63852.328125</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>64896.007812,64771.468750,64662.937500,64568.535156,64487.339844,64370.828125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>65216.22265625</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64018.28125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1197.94140625</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.871248935240666</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.305409109218568</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>63924.9453125</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>65269.843750,65241.605469,65240.070312,65211.808594,65250.128906,65216.222656</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>65453.988281,65027.648438,64031.101562,64158.339844,64083.320312,64018.281250</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>184.144531,213.957032,1208.968750,1053.468750,1166.808593,1197.941406</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.281334,0.329025,1.888096,1.641983,1.820768,1.871249</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.305409109218568</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>65178.515625,65221.792969,65206.812500,65201.917969,65111.105469,65076.378906</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>64896.007812,64771.468750,64662.937500,64568.535156,64487.339844,64370.828125</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:18</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>63990.675781,63946.402344,63958.097656,63959.148438,63945.390625,63924.945312</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>63886.078125,63960.535156,63871.187500,63986.097656,63909.238281,63866.132812</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>63295.066406,63074.644531,62945.968750,62799.675781,62678.484375,62557.308594</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>63536.210938,63423.183594,63336.507812,63271.347656,63162.402344,63061.621094</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>63924.9453125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>64508.01953125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>583.07421875</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9038786541377819</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.415511521670722</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>64643.48046875</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>63990.675781,63946.402344,63958.097656,63959.148438,63945.390625,63924.945312</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>63951.750000,64005.738281,64117.691406,64328.718750,64339.281250,64508.019531</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>38.925781,59.335937,159.593750,369.570312,393.890625,583.074219</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.060867,0.092704,0.248908,0.574503,0.612209,0.903879</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.415511521670722</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>63886.078125,63960.535156,63871.187500,63986.097656,63909.238281,63866.132812</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>63536.210938,63423.183594,63336.507812,63271.347656,63162.402344,63061.621094</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:42:12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>64552.503906,64568.785156,64578.570312,64601.089844,64647.894531,64643.480469</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>64490.339844,64588.015625,64528.082031,64557.335938,64570.242188,64559.757812</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>63985.152344,63882.886719,63797.964844,63732.402344,63684.535156,63620.917969</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>64220.441406,64155.851562,64102.480469,64074.097656,64058.667969,64027.765625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>64643.48046875</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65235.01953125</v>
+      </c>
+      <c r="H8" t="n">
+        <v>591.5390625</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9067814599436593</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.464565883261902</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65127.171875</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>64552.503906,64568.785156,64578.570312,64601.089844,64647.894531,64643.480469</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>64309.421875,64450.480469,64710.281250,64641.089844,65336.308594,65235.019531</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>243.082031,118.304687,131.710938,40.000000,688.414063,591.539062</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.377988,0.183559,0.203539,0.061880,1.053647,0.906781</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.464565883261902</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>64490.339844,64588.015625,64528.082031,64557.335938,64570.242188,64559.757812</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>64220.441406,64155.851562,64102.480469,64074.097656,64058.667969,64027.765625</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>65271.335938,65274.460938,65261.054688,65214.085938,65182.273438,65127.171875</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>65238.101562,65319.515625,65179.140625,65110.773438,65109.195312,64961.562500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>64654.710938,64504.265625,64369.132812,64206.179688,64093.484375,63957.328125</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>64868.125000,64793.851562,64696.218750,64590.078125,64479.187500,64412.593750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>65127.171875</v>
+      </c>
+      <c r="G9" t="n">
+        <v>63239.62109375</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1887.55078125</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.98475978920207</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.253004196956965</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:49</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63217.0234375</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>65271.335938,65274.460938,65261.054688,65214.085938,65182.273438,65127.171875</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>65165.101562,65040.320312,64475.171875,64919.308594,63693.570312,63239.621094</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>106.234375,234.140625,785.882813,294.777344,1488.703125,1887.550781</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.163023,0.359993,1.218892,0.454067,2.337289,2.984760</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.253004196956965</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>65238.101562,65319.515625,65179.140625,65110.773438,65109.195312,64961.562500</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>64868.125000,64793.851562,64696.218750,64590.078125,64479.187500,64412.593750</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:49</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>63235.792969,63175.312500,63131.871094,63143.523438,63177.871094,63217.023438</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>63149.937500,63245.531250,63093.695312,63110.726562,63204.871094,63220.589844</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>62319.472656,62038.402344,61776.878906,61586.695312,61482.980469,61361.734375</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>62676.027344,62494.363281,62304.621094,62226.640625,62151.398438,62128.078125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>63217.0234375</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63800.3515625</v>
+      </c>
+      <c r="H10" t="n">
+        <v>583.328125</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9143023677989627</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7263126268425654</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:49</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63997.9296875</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>63235.792969,63175.312500,63131.871094,63143.523438,63177.871094,63217.023438</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>63435.800781,63414.078125,63857.589844,63817.558594,63533.089844,63800.351562</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>200.007812,238.765625,725.718750,674.035156,355.218750,583.328125</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.315292,0.376518,1.136464,1.056191,0.559108,0.914302</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7263126268425654</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>63149.937500,63245.531250,63093.695312,63110.726562,63204.871094,63220.589844</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>62676.027344,62494.363281,62304.621094,62226.640625,62151.398438,62128.078125</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:49</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>63824.703125,63873.117188,63882.617188,63909.902344,63961.691406,63997.929688</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>63788.054688,63930.187500,63841.898438,63896.800781,63945.628906,63952.195312</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>63160.808594,63015.562500,62883.085938,62765.906250,62710.480469,62619.281250</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>63391.437500,63359.589844,63256.273438,63238.554688,63201.015625,63181.562500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>63997.9296875</v>
+      </c>
+      <c r="G11" t="n">
+        <v>64102.98828125</v>
+      </c>
+      <c r="H11" t="n">
+        <v>105.05859375</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1638903217570115</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4686851700895814</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>64273.34765625</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>63824.703125,63873.117188,63882.617188,63909.902344,63961.691406,63997.929688</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>64477.691406,64437.000000,63867.929688,63526.828125,63875.851562,64102.988281</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>652.988281,563.882812,14.687500,383.074219,85.839843,105.058593</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.012735,0.875092,0.022997,0.603012,0.134385,0.163890</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4686851700895814</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>63788.054688,63930.187500,63841.898438,63896.800781,63945.628906,63952.195312</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>63391.437500,63359.589844,63256.273438,63238.554688,63201.015625,63181.562500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:58:06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>64105.250000,64158.945312,64167.691406,64185.320312,64231.128906,64273.347656</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>64049.144531,64114.570312,64123.062500,64139.550781,64172.441406,64215.273438</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>63323.347656,63252.492188,63144.347656,63063.605469,63031.531250,62995.664062</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>63601.488281,63604.285156,63514.167969,63526.332031,63487.664062,63506.414062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>64273.34765625</v>
+      </c>
+      <c r="G12" t="n">
+        <v>64251.05078125</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22.296875</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.03470273984453926</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5865962402103819</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:58</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>64233.9375</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>64105.250000,64158.945312,64167.691406,64185.320312,64231.128906,64273.347656</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>63918.308594,64700.839844,64658.410156,64727.519531,64721.890625,64251.050781</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>186.941406,541.894532,490.718750,542.199219,490.761719,22.296875</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.292469,0.837539,0.758940,0.837664,0.758262,0.034703</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5865962402103819</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>64049.144531,64114.570312,64123.062500,64139.550781,64172.441406,64215.273438</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>63601.488281,63604.285156,63514.167969,63526.332031,63487.664062,63506.414062</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:58</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>64256.039062,64291.351562,64293.171875,64284.171875,64248.750000,64233.937500</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>64232.234375,64297.531250,64281.601562,64232.273438,64223.812500,64232.570312</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>63568.812500,63476.195312,63364.601562,63262.671875,63157.546875,63064.500000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>63828.406250,63787.039062,63694.546875,63650.117188,63561.007812,63518.179688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>64233.9375</v>
+      </c>
+      <c r="G13" t="n">
+        <v>62931.359375</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1302.578125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.069839485332109</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.779813384348964</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>63279.08984375</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>64256.039062,64291.351562,64293.171875,64284.171875,64248.750000,64233.937500</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>63872.109375,63738.750000,62625.761719,62892.000000,62825.820312,62931.359375</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>383.929687,552.601562,1667.410156,1392.171875,1422.929688,1302.578125</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.601091,0.866979,2.662499,2.213591,2.264880,2.069839</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.779813384348964</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>64232.234375,64297.531250,64281.601562,64232.273438,64223.812500,64232.570312</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>63828.406250,63787.039062,63694.546875,63650.117188,63561.007812,63518.179688</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:40:06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>62994.519531,63094.503906,63163.574219,63224.781250,63248.636719,63279.089844</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>63000.074219,63148.972656,63174.058594,63225.683594,63275.691406,63314.929688</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>62312.210938,62258.753906,62200.105469,62151.867188,62088.246094,62052.671875</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>62570.605469,62563.191406,62542.203125,62553.148438,62522.406250,62509.671875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>63279.08984375</v>
+      </c>
+      <c r="G14" t="n">
+        <v>63399.66015625</v>
+      </c>
+      <c r="H14" t="n">
+        <v>120.5703125</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1901750138768118</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4423562601213719</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63580.3984375</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>62994.519531,63094.503906,63163.574219,63224.781250,63248.636719,63279.089844</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>62988.589844,63016.468750,62938.820312,62471.531250,62766.671875,63399.660156</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5.929687,78.035156,224.753907,753.250000,481.964844,120.570312</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.009414,0.123833,0.357099,1.205749,0.767867,0.190175</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4423562601213719</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>63000.074219,63148.972656,63174.058594,63225.683594,63275.691406,63314.929688</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>62570.605469,62563.191406,62542.203125,62553.148438,62522.406250,62509.671875</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>63407.613281,63420.062500,63440.632812,63510.156250,63523.570312,63580.398438</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>63408.046875,63441.617188,63443.035156,63534.207031,63539.023438,63609.511719</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>62825.019531,62665.402344,62557.457031,62487.757812,62416.410156,62385.867188</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>63053.878906,62945.203125,62859.964844,62860.722656,62813.730469,62805.574219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>63580.3984375</v>
+      </c>
+      <c r="G15" t="n">
+        <v>62962.53125</v>
+      </c>
+      <c r="H15" t="n">
+        <v>617.8671875</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9813252028364092</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4425451227103662</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>63416.89453125</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>63407.613281,63420.062500,63440.632812,63510.156250,63523.570312,63580.398438</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>63448.261719,62964.218750,63041.429688,63380.179688,63493.351562,62962.531250</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>40.648438,455.843750,399.203125,129.976562,30.218750,617.867188</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.064065,0.723973,0.633239,0.205074,0.047594,0.981325</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4425451227103662</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>63408.046875,63441.617188,63443.035156,63534.207031,63539.023438,63609.511719</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>63053.878906,62945.203125,62859.964844,62860.722656,62813.730469,62805.574219</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:42:06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>63047.863281,63154.980469,63261.085938,63350.519531,63402.667969,63416.894531</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>63047.675781,63155.800781,63269.230469,63351.832031,63447.660156,63430.929688</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>62423.488281,62382.910156,62376.867188,62358.199219,62336.000000,62288.558594</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>62668.851562,62678.250000,62699.402344,62727.191406,62729.281250,62700.906250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>63416.89453125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>63660.6484375</v>
+      </c>
+      <c r="H16" t="n">
+        <v>243.75390625</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3828957326586295</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6130462353664323</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>63509.33984375</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>63047.863281,63154.980469,63261.085938,63350.519531,63402.667969,63416.894531</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>62524.601562,62481.289062,63624.261719,63802.781250,63466.519531,63660.648438</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>523.261718,673.691407,363.175781,452.261719,63.851562,243.753907</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.836889,1.078229,0.570813,0.708843,0.100607,0.382896</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6130462353664323</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>63047.675781,63155.800781,63269.230469,63351.832031,63447.660156,63430.929688</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>62668.851562,62678.250000,62699.402344,62727.191406,62729.281250,62700.906250</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>63664.156250,63634.320312,63581.792969,63574.796875,63502.980469,63509.339844</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>63668.148438,63617.503906,63583.722656,63550.214844,63528.324219,63503.539062</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>62977.523438,62802.406250,62620.117188,62512.390625,62358.988281,62301.687500</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>63249.335938,63125.218750,62974.781250,62915.046875,62786.980469,62753.914062</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>63509.33984375</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64065.1484375</v>
+      </c>
+      <c r="H17" t="n">
+        <v>555.80859375</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8675677920144521</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6763808162425077</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>63898.0859375</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>63664.156250,63634.320312,63581.792969,63574.796875,63502.980469,63509.339844</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>63617.410156,63853.320312,64068.738281,64181.000000,64189.621094,64065.148438</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>46.746094,219.000000,486.945312,606.203125,686.640625,555.808593</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.073480,0.342974,0.760036,0.944521,1.069707,0.867568</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6763808162425077</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>63668.148438,63617.503906,63583.722656,63550.214844,63528.324219,63503.539062</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>63249.335938,63125.218750,62974.781250,62915.046875,62786.980469,62753.914062</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:21:09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>64014.789062,63973.765625,63939.453125,63904.566406,63876.062500,63898.085938</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>63991.253906,63914.781250,63927.347656,63873.507812,63884.941406,63861.746094</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>63454.023438,63247.425781,63068.300781,62911.632812,62794.648438,62736.628906</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>63683.601562,63532.152344,63392.492188,63293.785156,63196.375000,63172.277344</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>63898.0859375</v>
+      </c>
+      <c r="G18" t="n">
+        <v>64470.26171875</v>
+      </c>
+      <c r="H18" t="n">
+        <v>572.17578125</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.887503425604356</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7001608030600708</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>64426.8359375</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>64014.789062,63973.765625,63939.453125,63904.566406,63876.062500,63898.085938</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>64109.980469,64018.289062,64328.250000,64794.628906,64597.859375,64470.261719</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>95.191407,44.523438,388.796875,890.062500,721.796875,572.175781</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.148481,0.069548,0.604395,1.373667,1.117370,0.887503</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7001608030600708</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>63991.253906,63914.781250,63927.347656,63873.507812,63884.941406,63861.746094</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>63683.601562,63532.152344,63392.492188,63293.785156,63196.375000,63172.277344</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>64443.671875,64436.500000,64417.656250,64397.640625,64395.703125,64426.835938</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>64411.023438,64359.687500,64383.960938,64351.656250,64383.023438,64343.687500</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>63911.476562,63781.257812,63642.710938,63505.773438,63426.250000,63387.242188</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>64135.796875,64049.171875,63935.390625,63858.539062,63788.117188,63781.101562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>64426.8359375</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64319.359375</v>
+      </c>
+      <c r="H19" t="n">
+        <v>107.4765625</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1670983099713126</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2081864266820184</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>64362.38671875</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>64443.671875,64436.500000,64417.656250,64397.640625,64395.703125,64426.835938</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>64744.410156,64552.621094,64570.921875,64397.949219,64267.300781,64319.359375</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>300.738281,116.121094,153.265625,0.308594,128.402344,107.476563</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.464501,0.179886,0.237360,0.000479,0.199794,0.167098</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2081864266820184</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>64411.023438,64359.687500,64383.960938,64351.656250,64383.023438,64343.687500</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>64135.796875,64049.171875,63935.390625,63858.539062,63788.117188,63781.101562</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:11:07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>64336.937500,64344.292969,64357.703125,64363.820312,64365.601562,64362.386719</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>64306.324219,64285.191406,64350.960938,64353.140625,64366.988281,64313.917969</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>63815.765625,63715.246094,63627.347656,63542.933594,63489.523438,63429.027344</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>64039.359375,63974.082031,63907.289062,63875.136719,63822.121094,63794.382812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>64362.38671875</v>
+      </c>
+      <c r="G20" t="n">
+        <v>64873.828125</v>
+      </c>
+      <c r="H20" t="n">
+        <v>511.44140625</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.788363229104572</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7336637084676191</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>64650.43359375</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>64336.937500,64344.292969,64357.703125,64363.820312,64365.601562,64362.386719</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>64264.191406,64975.628906,64852.910156,64914.789062,64960.921875,64873.828125</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>72.746094,631.335937,495.207031,550.968750,595.320313,511.441406</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.113198,0.971650,0.763585,0.848757,0.916428,0.788363</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7336637084676191</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>64306.324219,64285.191406,64350.960938,64353.140625,64366.988281,64313.917969</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>64039.359375,63974.082031,63907.289062,63875.136719,63822.121094,63794.382812</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:08:08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>64850.742188,64836.820312,64787.085938,64737.902344,64703.675781,64650.433594</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>64797.535156,64766.042969,64747.093750,64687.437500,64663.894531,64581.054688</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>64385.437500,64263.093750,64100.074219,63962.933594,63852.992188,63731.585938</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>64596.398438,64506.496094,64380.835938,64289.433594,64189.484375,64096.855469</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>64650.43359375</v>
+      </c>
+      <c r="G21" t="n">
+        <v>64782.26953125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>131.8359375</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.203506203864013</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2636706080156673</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>64692.6640625</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>64850.742188,64836.820312,64787.085938,64737.902344,64703.675781,64650.433594</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>64928.800781,64922.839844,65029.660156,65025.421875,64905.281250,64782.269531</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>78.058593,86.019532,242.574218,287.519531,201.605469,131.835937</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.120222,0.132495,0.373021,0.442165,0.310615,0.203506</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2636706080156673</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>64797.535156,64766.042969,64747.093750,64687.437500,64663.894531,64581.054688</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>64596.398438,64506.496094,64380.835938,64289.433594,64189.484375,64096.855469</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:19:11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>64741.109375,64734.390625,64716.156250,64704.429688,64712.843750,64692.664062</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>64715.164062,64688.335938,64694.929688,64659.898438,64681.015625,64610.703125</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>64272.367188,64158.265625,64047.484375,63958.960938,63926.101562,63836.101562</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>64481.109375,64406.046875,64321.937500,64279.546875,64240.015625,64188.632812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>64692.6640625</v>
+      </c>
+      <c r="G22" t="n">
+        <v>64910.23828125</v>
+      </c>
+      <c r="H22" t="n">
+        <v>217.57421875</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3351924511619742</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3673828258027115</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64856.0078125</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>64741.109375,64734.390625,64716.156250,64704.429688,64712.843750,64692.664062</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>64770.871094,64899.968750,65174.988281,65130.738281,64848.691406,64910.238281</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>29.761719,165.578125,458.832031,426.308593,135.847656,217.574219</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.045949,0.255128,0.704000,0.654543,0.209484,0.335192</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3673828258027115</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>64715.164062,64688.335938,64694.929688,64659.898438,64681.015625,64610.703125</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>64481.109375,64406.046875,64321.937500,64279.546875,64240.015625,64188.632812</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>64931.808594,64918.921875,64880.242188,64875.359375,64867.449219,64856.007812</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>64891.441406,64874.042969,64850.382812,64832.347656,64819.703125,64762.359375</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>64531.597656,64416.800781,64288.503906,64204.187500,64142.691406,64068.320312</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>64705.753906,64628.863281,64525.171875,64492.789062,64433.464844,64385.535156</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>64856.0078125</v>
+      </c>
+      <c r="G23" t="n">
+        <v>63979.9609375</v>
+      </c>
+      <c r="H23" t="n">
+        <v>876.046875</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.369251969152939</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9686219308707882</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>64214.703125</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>64931.808594,64918.921875,64880.242188,64875.359375,64867.449219,64856.007812</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>65149.839844,65069.460938,64235.851562,63975.878906,63929.390625,63979.960938</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>218.031250,150.539062,644.390625,899.480469,938.058594,876.046875</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.334661,0.231351,1.003164,1.405968,1.467335,1.369252</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9686219308707882</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>64891.441406,64874.042969,64850.382812,64832.347656,64819.703125,64762.359375</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>64705.753906,64628.863281,64525.171875,64492.789062,64433.464844,64385.535156</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:15:04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>64001.351562,64053.773438,64126.937500,64169.554688,64211.500000,64214.703125</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>63982.468750,64071.726562,64156.460938,64194.789062,64215.460938,64190.367188</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>63506.296875,63425.304688,63395.835938,63331.398438,63309.375000,63243.703125</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>63724.671875,63682.109375,63672.210938,63679.757812,63657.773438,63618.242188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>64214.703125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>63788.48828125</v>
+      </c>
+      <c r="H24" t="n">
+        <v>426.21484375</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6681689051334387</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7092391163639651</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>63973.390625</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>64001.351562,64053.773438,64126.937500,64169.554688,64211.500000,64214.703125</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>63999.171875,64327.171875,63541.371094,63477.968750,63482.839844,63788.488281</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.179687,273.398437,585.566406,691.585938,728.660156,426.214844</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.003406,0.425012,0.921551,1.089490,1.147806,0.668169</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7092391163639651</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>63982.468750,64071.726562,64156.460938,64194.789062,64215.460938,64190.367188</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>63724.671875,63682.109375,63672.210938,63679.757812,63657.773438,63618.242188</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:50</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>63831.730469,63895.878906,63903.687500,63927.437500,63952.917969,63973.390625</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>63805.960938,63913.789062,63897.511719,63936.675781,63936.820312,63949.324219</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>63294.191406,63253.562500,63168.753906,63111.324219,63077.578125,63033.582031</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>63518.417969,63498.941406,63438.746094,63431.832031,63411.972656,63393.457031</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>63973.390625</v>
+      </c>
+      <c r="G25" t="n">
+        <v>63346.859375</v>
+      </c>
+      <c r="H25" t="n">
+        <v>626.53125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.989048638214355</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6901405855730836</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>63710.08984375</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>63831.730469,63895.878906,63903.687500,63927.437500,63952.917969,63973.390625</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>63767.031250,64175.898438,63368.640625,63345.718750,63413.058594,63346.859375</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>64.699219,280.019532,535.046875,581.718750,539.859375,626.531250</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.101462,0.436331,0.844340,0.918324,0.851338,0.989049</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.6901405855730836</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>63805.960938,63913.789062,63897.511719,63936.675781,63936.820312,63949.324219</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>63518.417969,63498.941406,63438.746094,63431.832031,63411.972656,63393.457031</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>63424.625000,63516.730469,63584.117188,63610.410156,63660.941406,63710.089844</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>63440.730469,63549.792969,63600.707031,63639.015625,63669.496094,63749.839844</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>62895.179688,62885.871094,62870.929688,62832.128906,62823.593750,62811.101562</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>63104.671875,63122.097656,63125.148438,63125.156250,63129.886719,63139.265625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>63710.08984375</v>
+      </c>
+      <c r="G26" t="n">
+        <v>63500.75</v>
+      </c>
+      <c r="H26" t="n">
+        <v>209.33984375</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3296651515926977</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3746121905632771</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>63660.546875</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>63424.625000,63516.730469,63584.117188,63610.410156,63660.941406,63710.089844</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>63803.980469,63414.898438,63358.121094,63335.078125,63425.351562,63500.750000</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>379.355469,101.832032,225.996094,275.332031,235.589843,209.339844</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.594564,0.160581,0.356696,0.434723,0.371444,0.329665</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3746121905632771</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>63440.730469,63549.792969,63600.707031,63639.015625,63669.496094,63749.839844</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>63104.671875,63122.097656,63125.148438,63125.156250,63129.886719,63139.265625</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:33:05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>63534.171875,63564.640625,63586.937500,63605.531250,63631.187500,63660.546875</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>63545.312500,63606.027344,63590.355469,63623.519531,63648.796875,63718.878906</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>63082.308594,63042.136719,62995.125000,62966.292969,62934.312500,62913.046875</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>63259.976562,63234.734375,63208.300781,63206.800781,63191.937500,63194.214844</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>63660.546875</v>
+      </c>
+      <c r="G27" t="n">
+        <v>62957.44140625</v>
+      </c>
+      <c r="H27" t="n">
+        <v>703.10546875</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.116794858630008</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.148214116368981</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>63183.72265625</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>63534.171875,63564.640625,63586.937500,63605.531250,63631.187500,63660.546875</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>62848.679688,62793.300781,62913.050781,62895.820312,62843.210938,62957.441406</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>685.492188,771.339844,673.886719,709.710938,787.976562,703.105469</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.090703,1.228379,1.071140,1.128391,1.253877,1.116795</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1.148214116368981</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>63545.312500,63606.027344,63590.355469,63623.519531,63648.796875,63718.878906</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>63259.976562,63234.734375,63208.300781,63206.800781,63191.937500,63194.214844</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:43:04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>63011.707031,63045.121094,63080.687500,63117.398438,63149.875000,63183.722656</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>63040.910156,63086.855469,63109.750000,63165.710938,63196.425781,63267.875000</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>62562.582031,62513.273438,62481.226562,62462.578125,62443.449219,62423.964844</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>62740.648438,62708.027344,62685.238281,62702.562500,62691.503906,62696.945312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>63183.72265625</v>
+      </c>
+      <c r="G28" t="n">
+        <v>62999.8515625</v>
+      </c>
+      <c r="H28" t="n">
+        <v>183.87109375</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2918595666334035</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1433357731931165</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>63077.36328125</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>63011.707031,63045.121094,63080.687500,63117.398438,63149.875000,63183.722656</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>63005.660156,62949.218750,63022.949219,63051.378906,63017.609375,62999.851562</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6.046875,95.902344,57.738281,66.019532,132.265625,183.871093</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.009597,0.152349,0.091615,0.104708,0.209887,0.291860</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1433357731931165</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>63040.910156,63086.855469,63109.750000,63165.710938,63196.425781,63267.875000</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>62740.648438,62708.027344,62685.238281,62702.562500,62691.503906,62696.945312</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:50:06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>63015.125000,63032.808594,63028.214844,63044.238281,63058.605469,63077.363281</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>63041.660156,63094.414062,63046.285156,63073.433594,63108.070312,63207.550781</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>62719.089844,62694.484375,62647.332031,62639.042969,62618.566406,62613.894531</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>62837.277344,62808.824219,62764.968750,62773.269531,62760.976562,62764.070312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>63077.36328125</v>
+      </c>
+      <c r="G29" t="n">
+        <v>63120.41015625</v>
+      </c>
+      <c r="H29" t="n">
+        <v>43.046875</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0681980280125566</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1402003044929188</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>63113.515625</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>63015.125000,63032.808594,63028.214844,63044.238281,63058.605469,63077.363281</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>62991.230469,62945.320312,63070.031250,63040.171875,62730.320312,63120.410156</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>23.894531,87.488282,41.816406,4.066406,328.285157,43.046875</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.037933,0.138991,0.066302,0.006450,0.523328,0.068198</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1402003044929188</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>63041.660156,63094.414062,63046.285156,63073.433594,63108.070312,63207.550781</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>62837.277344,62808.824219,62764.968750,62773.269531,62760.976562,62764.070312</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>63082.046875,63092.796875,63085.960938,63100.070312,63102.507812,63113.515625</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>63136.468750,63152.625000,63128.945312,63160.710938,63181.976562,63243.679688</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>62797.703125,62773.062500,62732.359375,62716.164062,62691.117188,62679.242188</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>62907.742188,62878.921875,62839.023438,62840.414062,62825.804688,62812.828125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>63113.515625</v>
+      </c>
+      <c r="G30" t="n">
+        <v>64200</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1086.484375</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.692343263239875</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.407307242488397</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:58</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>64125.55078125</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>63082.046875,63092.796875,63085.960938,63100.070312,63102.507812,63113.515625</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>63461.460938,63563.000000,64141.269531,64266.441406,64359.910156,64200.000000</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>379.414062,470.203125,1055.308593,1166.371094,1257.402344,1086.484375</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.597865,0.739743,1.645288,1.814899,1.953704,1.692343</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1.407307242488397</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>63136.468750,63152.625000,63128.945312,63160.710938,63181.976562,63243.679688</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>62907.742188,62878.921875,62839.023438,62840.414062,62825.804688,62812.828125</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:58</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>64164.863281,64162.542969,64120.121094,64133.917969,64128.062500,64125.550781</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>64186.636719,64146.761719,64126.140625,64098.363281,64113.863281,64128.789062</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>63750.492188,63656.843750,63527.015625,63475.074219,63397.351562,63314.023438</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>63921.117188,63843.308594,63737.289062,63721.007812,63667.410156,63609.636719</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>64125.55078125</v>
+      </c>
+      <c r="G31" t="n">
+        <v>64370.55859375</v>
+      </c>
+      <c r="H31" t="n">
+        <v>245.0078125</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3806209202661616</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5376885988565859</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:42</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>64435.55859375</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>64164.863281,64162.542969,64120.121094,64133.917969,64128.062500,64125.550781</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>64139.781250,64288.179688,64808.000000,64603.929688,64659.589844,64370.558594</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>25.082031,125.636718,687.878906,470.011718,531.527344,245.007813</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.039105,0.195427,1.061410,0.727528,0.822039,0.380621</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5376885988565859</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>64186.636719,64146.761719,64126.140625,64098.363281,64113.863281,64128.789062</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>63921.117188,63843.308594,63737.289062,63721.007812,63667.410156,63609.636719</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:42</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>64411.437500,64429.121094,64436.941406,64442.164062,64440.859375,64435.558594</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>64385.937500,64407.972656,64436.906250,64369.902344,64380.007812,64411.695312</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>63863.265625,63798.621094,63721.234375,63671.671875,63633.148438,63579.750000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>64079.769531,64034.230469,63995.617188,63979.250000,63953.894531,63906.675781</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>64435.55859375</v>
+      </c>
+      <c r="G32" t="n">
+        <v>69585.78125</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5150.22265625</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7.401257216250626</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.405947603304752</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:42</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>69245.953125</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>64411.437500,64429.121094,64436.941406,64442.164062,64440.859375,64435.558594</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>64243.550781,64459.109375,68519.632812,68406.132812,69271.429688,69585.781250</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>167.886719,29.988281,4082.691407,3963.968750,4830.570312,5150.222656</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.261329,0.046523,5.958426,5.794756,6.973395,7.401257</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4.405947603304752</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>64385.937500,64407.972656,64436.906250,64369.902344,64380.007812,64411.695312</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>64079.769531,64034.230469,63995.617188,63979.250000,63953.894531,63906.675781</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:42</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69637.468750,69542.132812,69340.890625,69256.734375,69212.875000,69245.953125</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>69498.164062,69291.734375,69225.578125,69003.468750,68942.796875,68911.218750</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>68401.804688,68029.734375,67569.640625,67211.648438,67020.218750,66928.171875</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>68884.781250,68643.804688,68259.664062,68045.484375,67842.703125,67790.218750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>69245.953125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>75370.7265625</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6124.7734375</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8.126196624124523</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.281139643222082</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>74542.984375</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>69637.468750,69542.132812,69340.890625,69256.734375,69212.875000,69245.953125</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>69783.609375,71875.273438,72439.671875,72627.921875,72998.320312,75370.726562</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>146.140625,2333.140626,3098.781250,3371.187500,3785.445312,6124.773438</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.209420,3.246096,4.277741,4.641724,5.185661,8.126197</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4.281139643222082</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>69498.164062,69291.734375,69225.578125,69003.468750,68942.796875,68911.218750</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>68884.781250,68643.804688,68259.664062,68045.484375,67842.703125,67790.218750</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:49:01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>75278.710938,75085.734375,74765.578125,74807.578125,74601.992188,74542.984375</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>75028.789062,74729.132812,74567.718750,74447.835938,74102.695312,74033.085938</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>73076.476562,72224.070312,71352.484375,70785.445312,70173.125000,69784.210938</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>73892.429688,73332.156250,72614.125000,72377.296875,71775.585938,71506.046875</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>74542.984375</v>
+      </c>
+      <c r="G34" t="n">
+        <v>77984.296875</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3441.3125</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.4128275023317</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.145095701422577</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>77508.953125</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>75278.710938,75085.734375,74765.578125,74807.578125,74601.992188,74542.984375</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>76288.117188,76709.632812,77191.796875,77003.921875,78546.851562,77984.296875</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1009.406249,1623.898438,2426.218750,2196.343750,3944.859374,3441.312500</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.323150,2.116942,3.143104,2.852249,5.022301,4.412828</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.145095701422577</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>75028.789062,74729.132812,74567.718750,74447.835938,74102.695312,74033.085938</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>73892.429688,73332.156250,72614.125000,72377.296875,71775.585938,71506.046875</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:42:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>77946.468750,77883.656250,77730.960938,77689.929688,77590.554688,77508.953125</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>77665.601562,77294.429688,77405.562500,77084.101562,76696.617188,76687.523438</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>76090.031250,75305.328125,74451.085938,73682.171875,73014.273438,72389.046875</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>76869.695312,76409.187500,75752.578125,75394.390625,74784.101562,74382.273438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>77508.953125</v>
+      </c>
+      <c r="G35" t="n">
+        <v>77236.546875</v>
+      </c>
+      <c r="H35" t="n">
+        <v>272.40625</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3526908711246032</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7223929284521146</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:58</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>77440.8984375</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>77946.468750,77883.656250,77730.960938,77689.929688,77590.554688,77508.953125</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>77286.242188,77114.351562,76970.562500,77419.937500,76979.992188,77236.546875</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>660.226562,769.304688,760.398438,269.992188,610.562501,272.406250</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.854261,0.997615,0.987908,0.348737,0.793144,0.352691</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.7223929284521146</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>77665.601562,77294.429688,77405.562500,77084.101562,76696.617188,76687.523438</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>76869.695312,76409.187500,75752.578125,75394.390625,74784.101562,74382.273438</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:58</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>77345.625000,77403.750000,77360.078125,77400.890625,77413.906250,77440.898438</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>77010.890625,77019.531250,77168.445312,77030.960938,76823.218750,76784.656250</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>75694.085938,75413.718750,74940.406250,74580.609375,74160.750000,73875.125000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>76404.882812,76279.484375,75912.046875,75848.093750,75546.890625,75356.500000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>77440.8984375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>77223.421875</v>
+      </c>
+      <c r="H36" t="n">
+        <v>217.4765625</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2816199505533761</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.499654227628428</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:37</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>77085.234375</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>77345.625000,77403.750000,77360.078125,77400.890625,77413.906250,77440.898438</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>75986.992188,77288.156250,77141.093750,77328.296875,77725.593750,77223.421875</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1358.632812,115.593750,218.984375,72.593750,311.687500,217.476563</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.787981,0.149562,0.283875,0.093877,0.401010,0.281620</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.499654227628428</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>77010.890625,77019.531250,77168.445312,77030.960938,76823.218750,76784.656250</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>76404.882812,76279.484375,75912.046875,75848.093750,75546.890625,75356.500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:37</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>77257.640625,77215.460938,77135.398438,77147.968750,77045.406250,77085.234375</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>77026.585938,76881.601562,76867.039062,76937.250000,76599.742188,76541.500000</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>75838.851562,75449.343750,74893.796875,74479.601562,73983.835938,73682.656250</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>76443.109375,76202.726562,75759.046875,75633.226562,75225.937500,75053.835938</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>77085.234375</v>
+      </c>
+      <c r="G37" t="n">
+        <v>79722.84375</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2637.609375</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.308473771045078</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.95180051712186</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:56</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="n">
+        <v>79923.125</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>77257.640625,77215.460938,77135.398438,77147.968750,77045.406250,77085.234375</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>77297.867188,78434.023438,79079.500000,78744.359375,78868.007812,79722.843750</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>40.226562,1218.562499,1944.101562,1596.390625,1822.601562,2637.609375</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.052041,1.553615,2.458414,2.027308,2.310952,3.308474</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.95180051712186</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>77026.585938,76881.601562,76867.039062,76937.250000,76599.742188,76541.500000</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>76443.109375,76202.726562,75759.046875,75633.226562,75225.937500,75053.835938</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:56</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>79765.515625,79795.046875,79858.015625,79988.750000,79952.875000,79923.125000</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79569.062500,79561.375000,79709.734375,79727.765625,79475.968750,79467.328125</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>78581.250000,78282.843750,77905.390625,77640.937500,77197.453125,76812.781250</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>79142.937500,78942.625000,78697.250000,78799.359375,78425.343750,78198.828125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>79923.125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>78822.5703125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1100.5546875</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.396243085117296</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9316432103220248</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>77834.9609375</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>79765.515625,79795.046875,79858.015625,79988.750000,79952.875000,79923.125000</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>79674.210938,79118.992188,79506.226562,78923.812500,78823.531250,78822.570312</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>91.304688,676.054688,351.789062,1064.937500,1129.343750,1100.554688</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.114598,0.854478,0.442467,1.349323,1.432750,1.396243</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9316432103220248</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>79569.062500,79561.375000,79709.734375,79727.765625,79475.968750,79467.328125</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>79142.937500,78942.625000,78697.250000,78799.359375,78425.343750,78198.828125</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>78612.156250,78482.156250,78394.867188,78284.390625,78062.015625,77834.960938</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>78220.820312,78037.882812,77706.039062,77611.226562,77150.343750,76510.843750</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>77368.117188,76617.921875,75736.023438,74866.843750,74028.882812,73155.328125</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>77886.109375,77343.992188,76774.437500,76319.703125,75681.085938,75017.250000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>77834.9609375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>78820.8203125</v>
+      </c>
+      <c r="H39" t="n">
+        <v>985.859375</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.250760105123716</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5985433985245976</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:29</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>79732.4765625</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>78612.156250,78482.156250,78394.867188,78284.390625,78062.015625,77834.960938</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>78915.976562,78467.421875,78013.359375,78463.007812,79026.179688,78820.820312</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>303.820312,14.734375,381.507813,178.617188,964.164062,985.859374</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.384992,0.018778,0.489029,0.227645,1.220057,1.250760</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.5985433985245976</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>78220.820312,78037.882812,77706.039062,77611.226562,77150.343750,76510.843750</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>77886.109375,77343.992188,76774.437500,76319.703125,75681.085938,75017.250000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:29</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>79813.140625,79722.007812,79695.945312,79713.789062,79710.218750,79732.476562</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>79681.312500,79619.195312,79101.046875,79504.921875,79346.578125,78968.265625</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>78951.093750,78430.484375,77939.664062,77483.007812,77073.890625,76832.234375</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>79350.429688,79011.304688,78647.406250,78514.593750,78320.031250,78116.804688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>79732.4765625</v>
+      </c>
+      <c r="G40" t="n">
+        <v>79649.1875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>83.2890625</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1045698834027654</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3157902788785527</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>79532.7890625</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>79813.140625,79722.007812,79695.945312,79713.789062,79710.218750,79732.476562</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>80320.570312,79932.531250,80269.390625,79824.703125,79677.000000,79649.187500</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>507.429688,210.523438,573.445313,110.914063,33.218750,83.289062</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.631756,0.263376,0.714401,0.138947,0.041692,0.104570</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.3157902788785527</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>79681.312500,79619.195312,79101.046875,79504.921875,79346.578125,78968.265625</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>79350.429688,79011.304688,78647.406250,78514.593750,78320.031250,78116.804688</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>79793.515625,79718.773438,79607.554688,79741.453125,79634.437500,79532.789062</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>79769.539062,79636.882812,79265.171875,79375.726562,79597.492188,79136.976562</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>78895.734375,78570.484375,78108.703125,78030.539062,77604.546875,77445.882812</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>79237.304688,79054.195312,78657.281250,78767.710938,78550.117188,78291.398438</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>79532.7890625</v>
+      </c>
+      <c r="G41" t="n">
+        <v>77469.203125</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2063.5859375</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.663750050675379</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.552704510456796</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="n">
+        <v>76454.71875</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>79793.515625,79718.773438,79607.554688,79741.453125,79634.437500,79532.789062</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>78324.226562,77533.640625,77838.671875,77501.046875,77469.203125,77469.203125</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1469.289062,2185.132813,1768.882813,2240.406250,2165.234375,2063.585937</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1.875906,2.818303,2.272499,2.890808,2.794961,2.663750</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.552704510456796</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>79769.539062,79636.882812,79265.171875,79375.726562,79597.492188,79136.976562</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>79237.304688,79054.195312,78657.281250,78767.710938,78550.117188,78291.398438</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:52:01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>77492.500000,77193.296875,76967.851562,76978.609375,76715.265625,76454.718750</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>77452.132812,77038.953125,76743.218750,76486.226562,76397.101562,75999.812500</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>76430.750000,75784.921875,75088.179688,74763.976562,74073.960938,73569.671875</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>76847.546875,76359.953125,75764.203125,75685.906250,75207.757812,74719.218750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>76454.71875</v>
+      </c>
+      <c r="G42" t="n">
+        <v>78168.84375</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1714.125</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.192849372931911</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.356614341724091</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:45</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="n">
+        <v>77887.359375</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>77492.500000,77193.296875,76967.851562,76978.609375,76715.265625,76454.718750</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>77575.406250,77855.578125,78193.601562,78233.929688,78135.101562,78168.843750</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>82.906250,662.281250,1225.750001,1255.320312,1419.835938,1714.125000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.106872,0.850654,1.567584,1.604573,1.817155,2.192849</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1.356614341724091</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>77452.132812,77038.953125,76743.218750,76486.226562,76397.101562,75999.812500</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>76847.546875,76359.953125,75764.203125,75685.906250,75207.757812,74719.218750</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:45</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>78224.398438,78210.414062,78179.687500,78133.093750,77991.453125,77887.359375</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>78156.921875,77863.625000,77791.445312,77558.023438,77455.640625,77472.398438</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>77418.367188,76978.937500,76420.773438,76068.523438,75483.500000,74990.148438</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>77818.179688,77584.507812,77191.734375,77045.921875,76563.421875,76182.406250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>77887.359375</v>
+      </c>
+      <c r="G43" t="n">
+        <v>77725.921875</v>
+      </c>
+      <c r="H43" t="n">
+        <v>161.4375</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.2077009781365169</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.4691689679404348</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>76365.0078125</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>78224.398438,78210.414062,78179.687500,78133.093750,77991.453125,77887.359375</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>78163.406250,78821.687500,78856.109375,77683.500000,77744.828125,77725.921875</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>60.992188,611.273438,676.421875,449.593750,246.625000,161.437500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.078032,0.775514,0.857793,0.578751,0.317224,0.207701</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.4691689679404348</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>78156.921875,77863.625000,77791.445312,77558.023438,77455.640625,77472.398438</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>77818.179688,77584.507812,77191.734375,77045.921875,76563.421875,76182.406250</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>77472.507812,77404.953125,77308.843750,77073.992188,76711.046875,76365.007812</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>77234.757812,77127.820312,76793.406250,76431.109375,76024.289062,75882.617188</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>76494.429688,75755.796875,75137.539062,74467.164062,73582.093750,72756.890625</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>76902.968750,76501.257812,76039.804688,75561.593750,74867.093750,74235.062500</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>76365.0078125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>78745.3125</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2380.3046875</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3.022789054904062</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.981300355817978</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>78352.875</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>77472.507812,77404.953125,77308.843750,77073.992188,76711.046875,76365.007812</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>78286.968750,78559.078125,78878.859375,78562.726562,78653.929688,78745.312500</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>814.460938,1154.125000,1570.015625,1488.734374,1942.882812,2380.304688</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1.040353,1.469117,1.990414,1.894963,2.470166,3.022789</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.981300355817978</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>77234.757812,77127.820312,76793.406250,76431.109375,76024.289062,75882.617188</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>76902.968750,76501.257812,76039.804688,75561.593750,74867.093750,74235.062500</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:49:05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>78654.617188,78628.421875,78675.968750,78565.250000,78516.523438,78352.875000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>78517.453125,78383.132812,78445.851562,78089.343750,77894.726562,77912.812500</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>77806.851562,77395.882812,77140.046875,76761.273438,76360.617188,75881.148438</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>78189.000000,78000.062500,77818.953125,77595.414062,77305.875000,76973.359375</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>78352.875</v>
+      </c>
+      <c r="G45" t="n">
+        <v>77327.390625</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1025.484375</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.326159290662086</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.308913560011824</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:14</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="n">
+        <v>76884.8828125</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>78654.617188,78628.421875,78675.968750,78565.250000,78516.523438,78352.875000</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>78061.710938,77881.429688,77267.890625,77258.843750,77512.453125,77327.390625</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>592.906251,746.992188,1408.078125,1306.406250,1004.070313,1025.484375</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.759535,0.959140,1.822333,1.690947,1.295366,1.326159</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.308913560011824</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>78517.453125,78383.132812,78445.851562,78089.343750,77894.726562,77912.812500</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>78189.000000,78000.062500,77818.953125,77595.414062,77305.875000,76973.359375</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:14</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>77174.468750,77174.789062,77120.828125,77053.296875,76991.648438,76884.882812</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>77114.445312,77040.125000,76993.148438,76721.734375,76707.789062,76612.585938</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>76415.289062,76178.093750,75842.492188,75627.484375,75246.375000,74842.429688</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>76702.312500,76629.703125,76373.218750,76220.968750,75937.476562,75761.140625</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>76884.8828125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>77724.03125</v>
+      </c>
+      <c r="H46" t="n">
+        <v>839.1484375</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.079651201828263</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.5297669569194901</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>77298.8203125</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>77174.468750,77174.789062,77120.828125,77053.296875,76991.648438,76884.882812</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>76778.492188,77253.039062,77324.640625,77316.101562,77673.960938,77724.031250</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>395.976562,78.250001,203.812500,262.804688,682.312499,839.148438</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.515739,0.101291,0.263580,0.339909,0.878431,1.079651</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.5297669569194901</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>77114.445312,77040.125000,76993.148438,76721.734375,76707.789062,76612.585938</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>76702.312500,76629.703125,76373.218750,76220.968750,75937.476562,75761.140625</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:07:12</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>77543.914062,77502.312500,77546.148438,77431.593750,77428.632812,77298.820312</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>77424.851562,77381.062500,77504.859375,77177.460938,77103.773438,77157.804688</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>76748.148438,76535.734375,76405.984375,76270.648438,76021.210938,75651.843750</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>77045.007812,76958.476562,76881.882812,76744.476562,76565.882812,76410.742188</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>77298.8203125</v>
+      </c>
+      <c r="G47" t="n">
+        <v>80872.6484375</v>
+      </c>
+      <c r="H47" t="n">
+        <v>3573.828125</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.419081350800482</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.956533140090183</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:52</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>80354.8671875</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>77543.914062,77502.312500,77546.148438,77431.593750,77428.632812,77298.820312</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>77910.273438,81358.210938,81760.179688,81270.828125,80850.500000,80872.648438</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>366.359376,3855.898438,4214.031249,3839.234375,3421.867188,3573.828126</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.470232,4.739409,5.154136,4.724001,4.232339,4.419081</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3.956533140090183</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>77424.851562,77381.062500,77504.859375,77177.460938,77103.773438,77157.804688</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>77045.007812,76958.476562,76881.882812,76744.476562,76565.882812,76410.742188</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:52</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>80735.390625,80679.695312,80624.656250,80484.328125,80339.765625,80354.867188</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>80421.695312,80540.257812,80538.085938,80206.273438,80031.070312,80151.781250</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>79569.070312,79348.023438,79025.375000,78837.312500,78479.140625,78357.734375</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>79950.609375,79799.343750,79585.484375,79381.656250,79126.328125,79077.195312</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>80354.8671875</v>
+      </c>
+      <c r="G48" t="n">
+        <v>79585.78125</v>
+      </c>
+      <c r="H48" t="n">
+        <v>769.0859375</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9663609823519828</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.018689274852818</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>79154.2578125</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>80735.390625,80679.695312,80624.656250,80484.328125,80339.765625,80354.867188</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>81219.593750,79422.953125,79812.523438,79675.117188,79596.273438,79585.781250</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>484.203125,1256.742187,812.132812,809.210938,743.492188,769.085938</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.596165,1.582341,1.017551,1.015638,0.934079,0.966361</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.018689274852818</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>80421.695312,80540.257812,80538.085938,80206.273438,80031.070312,80151.781250</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>79950.609375,79799.343750,79585.484375,79381.656250,79126.328125,79077.195312</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:48</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>79540.132812,79420.515625,79323.125000,79252.210938,79133.078125,79154.257812</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>79343.898438,79308.195312,79299.085938,79048.367188,78911.742188,78908.718750</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>78763.937500,78444.406250,78072.656250,77899.117188,77498.562500,77364.460938</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>79070.750000,78828.882812,78586.554688,78422.867188,78143.960938,78101.726562</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>79154.2578125</v>
+      </c>
+      <c r="G49" t="n">
+        <v>79968.0078125</v>
+      </c>
+      <c r="H49" t="n">
+        <v>813.75</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1.017594438400903</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6695962878452443</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:39</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>79613.0546875</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>79540.132812,79420.515625,79323.125000,79252.210938,79133.078125,79154.257812</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>79621.921875,79802.007812,79753.210938,79856.648438,80031.867188,79968.007812</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>81.789063,381.492188,430.085938,604.437499,898.789062,813.750001</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.102722,0.478048,0.539271,0.756903,1.123039,1.017594</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.6695962878452443</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>79343.898438,79308.195312,79299.085938,79048.367188,78911.742188,78908.718750</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>79070.750000,78828.882812,78586.554688,78422.867188,78143.960938,78101.726562</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:39</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>79939.828125,79873.015625,79857.687500,79786.875000,79690.437500,79613.054688</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>79891.304688,79855.921875,79926.796875,79507.203125,79580.929688,79375.906250</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>79351.039062,79129.937500,78886.000000,78756.601562,78485.515625,78270.460938</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>79565.726562,79425.687500,79324.734375,79168.976562,78939.414062,78868.703125</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>79613.0546875</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79681.4921875</v>
+      </c>
+      <c r="H50" t="n">
+        <v>68.4375</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0858888282851913</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1943913849929196</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>79405.390625</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>79939.828125,79873.015625,79857.687500,79786.875000,79690.437500,79613.054688</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>79922.992188,79707.648438,79829.976562,80339.320312,79587.312500,79681.492188</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>16.835938,165.367188,27.710938,552.445312,103.125000,68.437499</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.021065,0.207467,0.034712,0.687640,0.129575,0.085889</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.1943913849929196</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>79891.304688,79855.921875,79926.796875,79507.203125,79580.929688,79375.906250</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>79565.726562,79425.687500,79324.734375,79168.976562,78939.414062,78868.703125</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>79567.703125,79643.484375,79594.828125,79470.031250,79497.218750,79405.390625</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>79468.609375,79586.828125,79710.843750,79228.890625,79240.234375,79090.890625</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>78860.562500,78791.656250,78507.296875,78255.937500,78040.578125,77885.968750</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>79147.578125,79151.812500,78969.875000,78733.765625,78592.468750,78475.468750</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>79405.390625</v>
+      </c>
+      <c r="G51" t="n">
+        <v>78786.0078125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>619.3828125</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.7861583924572584</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6047660042604817</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:43</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>78514.65625</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>79567.703125,79643.484375,79594.828125,79470.031250,79497.218750,79405.390625</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>79409.132812,78800.000000,79352.210938,79091.968750,78875.218750,78786.007812</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>158.570312,843.484375,242.617188,378.062500,622.000000,619.382812</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.199688,1.070412,0.305747,0.478004,0.788587,0.786158</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.6047660042604817</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>79468.609375,79586.828125,79710.843750,79228.890625,79240.234375,79090.890625</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>79147.578125,79151.812500,78969.875000,78733.765625,78592.468750,78475.468750</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:43</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>78823.023438,78855.921875,78721.960938,78689.078125,78570.796875,78514.656250</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>78740.015625,78932.734375,78803.453125,78507.539062,78590.640625,78310.625000</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>78180.281250,78122.226562,77830.414062,77777.406250,77481.726562,77408.125000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>78439.226562,78406.156250,78277.414062,78134.226562,77951.679688,77848.179688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>78514.65625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>78867.2578125</v>
+      </c>
+      <c r="H52" t="n">
+        <v>352.6015625</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.4470823156274551</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2957029449813864</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:20</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>78611.609375</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>78823.023438,78855.921875,78721.960938,78689.078125,78570.796875,78514.656250</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>78401.882812,78899.992188,78437.101562,78446.882812,78619.710938,78867.257812</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>421.140626,44.070312,284.859376,242.195312,48.914062,352.601562</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.537156,0.055856,0.363169,0.308738,0.062216,0.447082</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2957029449813864</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>78740.015625,78932.734375,78803.453125,78507.539062,78590.640625,78310.625000</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>78439.226562,78406.156250,78277.414062,78134.226562,77951.679688,77848.179688</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:20</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>78802.601562,78834.375000,78761.679688,78756.843750,78718.460938,78611.609375</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>78827.023438,78866.390625,78706.914062,78468.992188,78714.546875,78521.914062</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>78258.218750,78193.953125,77997.343750,77935.875000,77742.625000,77577.968750</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>78413.359375,78402.921875,78334.242188,78250.921875,78126.148438,78014.875000</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>78611.609375</v>
+      </c>
+      <c r="G53" t="n">
+        <v>78383.828125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>227.78125</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2905972513064218</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5216748063862058</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:09</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
+        <v>78210.5625</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>78802.601562,78834.375000,78761.679688,78756.843750,78718.460938,78611.609375</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>79294.257812,78576.406250,78211.257812,78248.812500,78297.148438,78383.828125</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>491.656251,257.968750,550.421876,508.031250,421.312501,227.781250</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.620040,0.328303,0.703763,0.649251,0.538094,0.290597</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5216748063862058</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>78827.023438,78866.390625,78706.914062,78468.992188,78714.546875,78521.914062</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>78413.359375,78402.921875,78334.242188,78250.921875,78126.148438,78014.875000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:20:09</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>78292.195312,78257.773438,78283.187500,78234.265625,78264.476562,78210.562500</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>78311.570312,78420.109375,78126.351562,78045.062500,78321.851562,78188.093750</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>77707.976562,77560.921875,77455.914062,77336.054688,77211.703125,77082.773438</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>77900.609375,77814.968750,77809.593750,77681.960938,77657.789062,77588.156250</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>78210.5625</v>
+      </c>
+      <c r="G54" t="n">
+        <v>76939.90625</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1270.65625</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1.65149180955754</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1.526426596691865</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:54</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>76658.34375</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>78292.195312,78257.773438,78283.187500,78234.265625,78264.476562,78210.562500</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>77820.750000,77218.742188,77119.531250,76531.953125,76863.656250,76939.906250</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>471.445312,1039.031251,1163.656250,1702.312500,1400.820312,1270.656250</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.605809,1.345569,1.508900,2.224316,1.822474,1.651492</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1.526426596691865</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>78311.570312,78420.109375,78126.351562,78045.062500,78321.851562,78188.093750</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>77900.609375,77814.968750,77809.593750,77681.960938,77657.789062,77588.156250</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:54</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>76758.125000,76643.320312,76651.960938,76658.773438,76749.695312,76658.343750</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>76703.937500,76688.250000,76403.093750,76529.609375,76774.687500,76574.843750</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>76274.375000,75980.968750,75815.968750,75708.640625,75638.109375,75418.484375</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>76401.000000,76230.640625,76151.937500,76087.218750,76069.234375,75957.429688</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/BTC-USD_4h_30d_h6/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>76658.34375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>77244.921875</v>
+      </c>
+      <c r="H55" t="n">
+        <v>586.578125</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.7593743520761377</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7666483531847794</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:07</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="n">
+        <v>77083.671875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>76758.125000,76643.320312,76651.960938,76658.773438,76749.695312,76658.343750</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>77014.882812,77694.351562,77256.617188,77208.640625,77259.226562,77244.921875</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>256.757812,1051.031251,604.656249,549.867187,509.531251,586.578125</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.333387,1.352777,0.782659,0.712183,0.659509,0.759374</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.7666483531847794</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>76703.937500,76688.250000,76403.093750,76529.609375,76774.687500,76574.843750</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>76401.000000,76230.640625,76151.937500,76087.218750,76069.234375,75957.429688</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:18:07</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BTC-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>77179.007812,77160.367188,77222.601562,77116.078125,77237.648438,77083.671875</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>77072.164062,77124.468750,76995.187500,77034.273438,77347.929688,76852.632812</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>76321.898438,76073.007812,76003.484375,75792.843750,75801.937500,75568.476562</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>76554.351562,76448.539062,76510.773438,76318.664062,76410.054688,76198.226562</t>
         </is>
       </c>
     </row>
